--- a/astro-site/public/dl/pack-appcc/12-analisis-peligros-haccp.xlsx
+++ b/astro-site/public/dl/pack-appcc/12-analisis-peligros-haccp.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Análisis Peligros" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análisis Peligros" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Análisis Peligros'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -126,39 +128,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -518,15 +520,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -534,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -541,9 +545,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -579,9 +581,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -589,9 +589,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -641,13 +639,19 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" t="inlineStr"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -655,7 +659,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -664,21 +677,21 @@
   <sheetPr>
     <tabColor rgb="00FF5722"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="12"/>
-    <col customWidth="1" max="3" min="3" width="25"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
-    <col customWidth="1" max="8" min="8" width="20"/>
-    <col customWidth="1" max="9" min="9" width="20"/>
-    <col customWidth="1" max="10" min="10" width="15"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,6 +708,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1547,6 +1561,7 @@
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
@@ -1573,17 +1588,25 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B18 B19 B20 B21 B22 B23 B24 B25 B26 B27" type="list">
+    <dataValidation sqref="B18 B19 B20 B21 B22 B23 B24 B25 B26 B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"B (Biológico),Q (Químico),F (Físico)"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" type="list">
+    <dataValidation sqref="D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F18 F19 F20 F21 F22 F23 F24 F25 F26 F27" type="list">
+    <dataValidation sqref="F18 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SÍ (PCC),NO"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/12-analisis-peligros-haccp.xlsx
+++ b/astro-site/public/dl/pack-appcc/12-analisis-peligros-haccp.xlsx
@@ -827,7 +827,7 @@
     <row r="32">
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>▸ Reg. (CE) 853/2004, Anexo III y RD 1420/2006 — congelación preventiva del pescado destinado a consumo en crudo (anisakis).</t>
+          <t>▸ RD 1021/2022, art. 8.1 —que derogó el RD 1420/2006— y Rgto. (CE) 853/2004, Anexo III, Secc. VIII, Cap. III.D — congelación preventiva del pescado destinado a consumo en crudo (anisakis). El art. 8.2 añade informar al consumidor con cartel o carta-menú.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="74" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>PREPARACIÓN</t>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>-20 °C durante al menos 24 h en todas las partes de la pieza, o -35 °C durante al menos 15 h (Reg. (CE) 853/2004, Anexo III + RD 1420/2006)</t>
+          <t>-20 °C durante al menos 24 h en todas las partes de la pieza, o -35 °C durante al menos 15 h (RD 1021/2022, art. 8.1, que derogó el RD 1420/2006, y Rgto. (CE) 853/2004, Anexo III, Secc. VIII, Cap. III.D)</t>
         </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
@@ -2629,8 +2629,8 @@
     <row r="51"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A45:M45"/>
     <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A45:M45"/>
     <mergeCell ref="A46:M46"/>
     <mergeCell ref="A41:M41"/>
     <mergeCell ref="A39:G39"/>
